--- a/data_extactor/batch_10_fa/trimmed/batch_0013_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0013_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | مخابرات | ریاضیات | امور اداری و دفتری</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | خدمات مشتری و شخصی | مهندسی و فناوری | مخابرات | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک کتبی | مرتب‌سازی اطلاعات | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شفاهی</t>
+          <t>حساسیت به مسئله | درک کتبی | ترتیب‌دهی اطلاعات | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شفاهی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>معماران شبکه کامپیوتری | کارشناسان پشتیبانی شبکه کامپیوتری | تحلیل‌گران سیستم‌های کامپیوتری | مدیران پایگاه داده | تحلیل‌گران امنیت اطلاعات | توسعه‌دهندگان نرم‌افزار | کارشناسان مهندسی مخابرات</t>
+          <t>معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | مدیران پایگاه داده | تحلیل‌گران امنیت اطلاعات | توسعه‌دهندگان نرم‌افزار | متخصصان مهندسی مخابرات</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | بیان کتبی</t>
+          <t>درک کتبی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>معماران شبکه کامپیوتری | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | مدیران پایگاه داده | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | توسعه‌دهندگان وب</t>
+          <t>معماران شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران پایگاه داده | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | توسعه‌دهندگان وب</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>توسعه‌دهنده برنامه‌های کاربردی | مهندس یکپارچه‌سازی نرم‌افزار | مهندس دواپس (DevOps Engineer) | توسعه‌دهنده نرم‌افزار | مهندس زیرساخت | معمار نرم‌افزار | توسعه‌دهنده نرم‌افزار | مهندس توسعه نرم‌افزار | مهندس نرم‌افزار | مهندس سیستم‌ها</t>
+          <t>توسعه‌دهنده برنامه‌های کاربردی | مهندس یکپارچه‌سازی نرم‌افزار | مهندس دواپس (DevOps Engineer) | توسعه‌دهنده نرم‌افزار | مهندس زیرساخت | معمار نرم‌افزار | مهندس توسعه نرم‌افزار | مهندس نرم‌افزار | مهندس سیستم‌ها</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | یادگیری فعال | شنیدن فعال | نگارش | سخن گفتن | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | یادگیری فعال | گوش دادن فعال | نگارش | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | ریاضیات | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | ریاضیات | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | استدلال استقرایی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | مدیران پایگاه داده | مهندسان امنیت اطلاعات | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | توسعه‌دهندگان وب</t>
+          <t>برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران پایگاه داده | مهندسان امنیت اطلاعات | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | توسعه‌دهندگان وب</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | تفکر انتقادی | شنیدن فعال | نگارش | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | سخن گفتن | تفکر انتقادی | گوش دادن فعال | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | کارشناسان تست نفوذ | کارشناسان کنترل کیفیت | توسعه‌دهندگان نرم‌افزار | طراحان وب و رابط‌های دیجیتال</t>
+          <t>برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان تحلیل کنترل کیفیت | توسعه‌دهندگان نرم‌افزار | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | یادگیری فعال | سخن گفتن | نگارش | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخن گفتن | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | ابتکار و اصالت</t>
+          <t>استدلال قیاسی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مدیران پایگاه داده | کارشناسان استراتژی بازاریابی جستجو | توسعه‌دهندگان نرم‌افزار | مدیران وب | طراحان وب و رابط‌های دیجیتال</t>
+          <t>برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مدیران پایگاه داده | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | توسعه‌دهندگان نرم‌افزار | مدیران وب | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | طراحی | زبان انگلیسی | ارتباطات و رسانه | خدمات مشتریان و خدمات فردی | هنرهای تجسمی</t>
+          <t>رایانه و الکترونیک | طراحی | زبان انگلیسی | ارتباطات و رسانه | خدمات مشتری و شخصی | هنرهای زیبا</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | مرتب‌سازی اطلاعات | حساسیت به مسئله | روانی ایده‌ها | ابتکار و اصالت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | روانی ایده‌ها | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>برنامه‌نویسان کامپیوتر | متخصصان نشر رومیزی | طراحان گرافیک | کارشناسان استراتژی بازاریابی جستجو | توسعه‌دهندگان نرم‌افزار | مدیران وب | توسعه‌دهندگان وب</t>
+          <t>برنامه‌نویسان کامپیوتر | متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | طراحان گرافیک | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | توسعه‌دهندگان نرم‌افزار | مدیران وب | توسعه‌دهندگان وب</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | نظارت | سخن گفتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>روانی ایده‌ها | درک کتبی | ابتکار و اصالت | مرتب‌سازی اطلاعات | بیان کتبی | حساسیت به مسئله | تجسم فضایی</t>
+          <t>روانی ایده‌ها | درک کتبی | اصالت | ترتیب‌دهی اطلاعات | بیان کتبی | حساسیت به مسئله | تجسم</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران هنری | برنامه‌نویسان کامپیوتر | تدوین‌گران فیلم و ویدیو | طراحان گرافیک | توسعه‌دهندگان نرم‌افزار | هنرمندان جلوه‌های ویژه و انیماتورها | طراحان وب و رابط‌های دیجیتال</t>
+          <t>مدیران هنری | برنامه‌نویسان کامپیوتر | تدوین‌گران فیلم و ویدیو | طراحان گرافیک | توسعه‌دهندگان نرم‌افزار | پویانماها و طراحان جلوه‌های ویژه | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | مخابرات | مدیریت و امور اداری</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | مخابرات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مهندسان امنیت اطلاعات | مدیران پروژه فناوری اطلاعات | تحلیل‌گران سیستم‌های کامپیوتری | مدیران شبکه و سیستم‌های کامپیوتری | توسعه‌دهندگان نرم‌افزار | برنامه‌نویسان کامپیوتر | توسعه‌دهندگان وب</t>
+          <t>مهندسان امنیت اطلاعات | مدیران پروژه‌های فناوری اطلاعات | تحلیل‌گران سیستم‌های کامپیوتری | مدیران شبکه و سیستم‌های کامپیوتری | توسعه‌دهندگان نرم‌افزار | برنامه‌نویسان کامپیوتر | توسعه‌دهندگان وب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نظارت | نگارش | سخن گفتن | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | طراحی</t>
+          <t>رایانه و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | خدمات مشتری و شخصی | مهندسی و فناوری | طراحی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>برنامه‌نویسان کامپیوتر | تحلیل‌گران امنیت اطلاعات | مدیران پروژه فناوری اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان استراتژی بازاریابی جستجو | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال</t>
+          <t>برنامه‌نویسان کامپیوتر | تحلیل‌گران امنیت اطلاعات | مدیران پروژه‌های فناوری اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | ریاضیات | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | ریاضیات | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | تجسم فضایی</t>
+          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | تجسم</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نقشه‌نگاران و متخصصان فتوگرامتری | دانشمندان داده | مدیران پایگاه داده | نقشه‌برداران ژئودتیک | جغرافیدانان | کارشناسان و متخصصان سنجش از دور | تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
+          <t>کارشناسان نقشه‌نگاری و فتوگرامتری | دانشمندان داده | مدیران پایگاه داده | مهندسان نقشه‌برداری ژئودزی | جغرافیدانان | دانشمندان و فناوران سنجش از دور | تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
